--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FA2A72-F333-47C5-846F-75EA84F2115F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003D1CDC-31D8-4106-8649-00292C86A817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1015</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1028</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="307">
   <si>
     <t>Account Name</t>
   </si>
@@ -1014,10 +1014,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1332,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1015"/>
+  <dimension ref="A1:C1029"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -12505,8 +12506,162 @@
         <v>122</v>
       </c>
     </row>
+    <row r="1016" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1016" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1016" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1016" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1017" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1017" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1017" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1018" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1018" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1018" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1019" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1019" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1019" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1020" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1020" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1020" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1021" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1021" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1021" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1022" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1022" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1022" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1023" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1023" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1023" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1024" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1024" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1024" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1025" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1025" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1025" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1026" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1026" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1026" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1027" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1027" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1027" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1028" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1028" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1029" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1029" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1015" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
+  <autoFilter ref="A1:C1028" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003D1CDC-31D8-4106-8649-00292C86A817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC4FE0-7F05-40E0-94CC-0EC329956543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="308">
   <si>
     <t>Account Name</t>
   </si>
@@ -958,6 +958,9 @@
   </si>
   <si>
     <t>ICR for the year</t>
+  </si>
+  <si>
+    <t>AIP-0109-Education Innovation-Google Cloud</t>
   </si>
 </sst>
 </file>
@@ -1014,11 +1017,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1333,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1029"/>
+  <dimension ref="A1:C1030"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -12631,7 +12633,7 @@
       <c r="A1027" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B1027" s="3" t="s">
+      <c r="B1027" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C1027" s="1" t="s">
@@ -12639,7 +12641,7 @@
       </c>
     </row>
     <row r="1028" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A1028" s="3" t="s">
+      <c r="A1028" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B1028" s="1" t="s">
@@ -12658,6 +12660,17 @@
       </c>
       <c r="C1029" s="1" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1030" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1030" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1030" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC4FE0-7F05-40E0-94CC-0EC329956543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4879902-32E8-4FF7-A759-925D809E009A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="309">
   <si>
     <t>Account Name</t>
   </si>
@@ -961,6 +961,9 @@
   </si>
   <si>
     <t>AIP-0109-Education Innovation-Google Cloud</t>
+  </si>
+  <si>
+    <t>AIP-0118-Training Infra and MEL-Google Digital-NFC</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1030"/>
+  <dimension ref="A1:C1053"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -12673,6 +12676,259 @@
         <v>97</v>
       </c>
     </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1031" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1031" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1032" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1032" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1033" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1033" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1034" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1034" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1035" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1035" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1036" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1036" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1037" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1038" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1038" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1039" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1039" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1040" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1041" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1042" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1043" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1044" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1045" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1046" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1047" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1048" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1049" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1050" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1051" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1052" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1052" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1053" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1053" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1028" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4879902-32E8-4FF7-A759-925D809E009A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7CC2FB-265B-4764-A3E7-ADA2056A0E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3159" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3258" uniqueCount="317">
   <si>
     <t>Account Name</t>
   </si>
@@ -964,13 +964,37 @@
   </si>
   <si>
     <t>AIP-0118-Training Infra and MEL-Google Digital-NFC</t>
+  </si>
+  <si>
+    <t>AIP-0141-Training Infra and MEL-Google-NFC</t>
+  </si>
+  <si>
+    <t>AIP-0132-Skill Development-GoogleDigital-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0137-SEAP-Google Digital-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0142-Ecosystem Building-Google India-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0139-SEAP-GOC-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0138-SEAP-Google Cloud-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0140-SEAP-Google Connect-Non FCRA</t>
+  </si>
+  <si>
+    <t>AIP-0112-Training Infra and MEL-Google Cloud-NFC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -981,6 +1005,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Lato"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Lato"/>
       <family val="2"/>
     </font>
@@ -1020,10 +1050,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1338,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1053"/>
+  <dimension ref="A1:C1086"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -12683,7 +12714,7 @@
       <c r="B1031" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1031" t="s">
+      <c r="C1031" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12694,7 +12725,7 @@
       <c r="B1032" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C1032" t="s">
+      <c r="C1032" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12705,7 +12736,7 @@
       <c r="B1033" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1033" t="s">
+      <c r="C1033" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12716,7 +12747,7 @@
       <c r="B1034" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1034" t="s">
+      <c r="C1034" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12727,7 +12758,7 @@
       <c r="B1035" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1035" t="s">
+      <c r="C1035" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12738,7 +12769,7 @@
       <c r="B1036" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C1036" t="s">
+      <c r="C1036" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12749,7 +12780,7 @@
       <c r="B1037" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1037" t="s">
+      <c r="C1037" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12760,7 +12791,7 @@
       <c r="B1038" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1038" t="s">
+      <c r="C1038" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12771,7 +12802,7 @@
       <c r="B1039" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1039" t="s">
+      <c r="C1039" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12782,7 +12813,7 @@
       <c r="B1040" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1040" t="s">
+      <c r="C1040" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12793,7 +12824,7 @@
       <c r="B1041" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1041" t="s">
+      <c r="C1041" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12804,7 +12835,7 @@
       <c r="B1042" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1042" t="s">
+      <c r="C1042" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12815,7 +12846,7 @@
       <c r="B1043" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1043" t="s">
+      <c r="C1043" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12826,7 +12857,7 @@
       <c r="B1044" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C1044" t="s">
+      <c r="C1044" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12837,7 +12868,7 @@
       <c r="B1045" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C1045" t="s">
+      <c r="C1045" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12848,7 +12879,7 @@
       <c r="B1046" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C1046" t="s">
+      <c r="C1046" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12859,7 +12890,7 @@
       <c r="B1047" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C1047" t="s">
+      <c r="C1047" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12870,7 +12901,7 @@
       <c r="B1048" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1048" t="s">
+      <c r="C1048" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12881,7 +12912,7 @@
       <c r="B1049" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C1049" t="s">
+      <c r="C1049" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12892,7 +12923,7 @@
       <c r="B1050" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C1050" t="s">
+      <c r="C1050" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12903,7 +12934,7 @@
       <c r="B1051" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C1051" t="s">
+      <c r="C1051" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -12914,7 +12945,7 @@
       <c r="B1052" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C1052" t="s">
+      <c r="C1052" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -12925,7 +12956,370 @@
       <c r="B1053" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1053" t="s">
+      <c r="C1053" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1054" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1054" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1055" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1055" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1056" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1056" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1057" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1057" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1058" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1058" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1059" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1059" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1060" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1060" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1061" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1061" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1061" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1062" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1062" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1062" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1063" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1063" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1063" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1064" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1064" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1064" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1065" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1065" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1065" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1066" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1066" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1066" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1067" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1067" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1067" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1068" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1068" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1068" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1069" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1069" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1069" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1070" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1070" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1070" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1071" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1071" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1071" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1072" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1072" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1072" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1073" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1073" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1073" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1074" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1074" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1074" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1075" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1075" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1075" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1076" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1076" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1076" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1077" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1077" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1077" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1078" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1078" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1078" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1079" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1079" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1079" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1080" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1080" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1080" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1081" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1081" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1081" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1082" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1082" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1082" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1083" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1083" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1083" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1084" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1084" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1084" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1085" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1085" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1085" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1086" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1086" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1086" s="2" t="s">
         <v>97</v>
       </c>
     </row>

--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9732F65-010A-4D8A-B9F7-35A3BCE05F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD575B0-0EF2-4F24-A21B-75EBA5FE5964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12216" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1032</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="323">
   <si>
     <t>Account Name</t>
   </si>
@@ -997,6 +997,15 @@
   </si>
   <si>
     <t>SECURITY DEPOSIT - STPI</t>
+  </si>
+  <si>
+    <t>AIP-0125-Generative AI-Google</t>
+  </si>
+  <si>
+    <t>TDS PAYABLE 194H</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1090"/>
+  <dimension ref="A1:C1103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -13376,8 +13385,151 @@
         <v>97</v>
       </c>
     </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1091" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1091" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1091" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1092" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1092" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1092" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1093" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1093" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1093" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1094" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1094" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1094" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1095" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1095" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1095" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1096" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1096" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1096" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1097" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1097" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1097" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1098" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1098" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1098" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1099" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1099" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1099" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1100" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1100" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1100" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1101" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1101" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1101" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1102" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1102" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1102" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1103" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1103" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1103" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1032" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
+  <autoFilter ref="A1:C1103" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>